--- a/General Optimization/Hexagon Weekend Sweep.xlsx
+++ b/General Optimization/Hexagon Weekend Sweep.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Snapping Arches\5 - Chiral 2D System\Github Code\2D-Array-Publication\General Optimization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5008571A-93B6-4480-A094-0EEA03263976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41EFD3F5-D7A8-4CE1-A0CA-6CD2DFD83F39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D361D6D6-5CA5-4995-899B-1D8B7FDBC61D}"/>
   </bookViews>
@@ -1777,7 +1777,7 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="752804" y="41623593"/>
+          <a:off x="752476" y="41624250"/>
           <a:ext cx="1906426" cy="1351409"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4668,7 +4668,7 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="4908330" y="41602572"/>
+          <a:off x="4905702" y="41603229"/>
           <a:ext cx="1906425" cy="1351408"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
